--- a/data.mn/public/datasets/hospital-beds-by-type.xlsx
+++ b/data.mn/public/datasets/hospital-beds-by-type.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,18 +418,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>department</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>hospital_beds</t>
         </is>
       </c>
     </row>
@@ -516,6 +517,126 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>Ophtalmology</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>тасаг</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>эмнэлгийн_ор</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Дотрын өвчин</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7564</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Хүүхдийн</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Мэс засал, гэмтлийн</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Мэдрэлийн</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Акушерийн</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Эхийн өвчний</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Сэтгэцийн болон нарколог</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Чих, хамар, хоолойн</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Нүдний</t>
         </is>
       </c>
       <c r="B10" t="n">
